--- a/Fig4/Fig4.xlsx
+++ b/Fig4/Fig4.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Summer" sheetId="3" r:id="rId3"/>
     <sheet name="Autumn" sheetId="4" r:id="rId4"/>
     <sheet name="Winter" sheetId="5" r:id="rId5"/>
+    <sheet name="Exclusion_summary" sheetId="6" r:id="rId6"/>
+    <sheet name="Annual_excluded_by_biome" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1775,4 +1777,492 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>total_valid_records</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_emission_lt0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>percent_emission_lt0</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_emission_lt0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>median_emission_lt0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1063</v>
+      </c>
+      <c r="C2">
+        <v>114</v>
+      </c>
+      <c r="D2">
+        <v>10.72</v>
+      </c>
+      <c r="E2">
+        <v>-57.038</v>
+      </c>
+      <c r="F2">
+        <v>-10.169</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Autumn</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1011</v>
+      </c>
+      <c r="C3">
+        <v>99</v>
+      </c>
+      <c r="D3">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E3">
+        <v>-52.313</v>
+      </c>
+      <c r="F3">
+        <v>-5.034</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1000</v>
+      </c>
+      <c r="C4">
+        <v>109</v>
+      </c>
+      <c r="D4">
+        <v>10.9</v>
+      </c>
+      <c r="E4">
+        <v>-30.607</v>
+      </c>
+      <c r="F4">
+        <v>-3.753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Summer</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1480</v>
+      </c>
+      <c r="C5">
+        <v>184</v>
+      </c>
+      <c r="D5">
+        <v>12.43</v>
+      </c>
+      <c r="E5">
+        <v>-270.649</v>
+      </c>
+      <c r="F5">
+        <v>-10.084</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>873</v>
+      </c>
+      <c r="C6">
+        <v>112</v>
+      </c>
+      <c r="D6">
+        <v>12.83</v>
+      </c>
+      <c r="E6">
+        <v>-47.1</v>
+      </c>
+      <c r="F6">
+        <v>-6.707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>total_valid_records</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_emission_lt0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>percent_emission_lt0</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_emission_lt0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>median_emission_lt0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>269</v>
+      </c>
+      <c r="C2">
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <v>17.84</v>
+      </c>
+      <c r="E2">
+        <v>-11.405</v>
+      </c>
+      <c r="F2">
+        <v>-6.61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>temperate seasonal forest</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>374</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>5.88</v>
+      </c>
+      <c r="E3">
+        <v>-49.644</v>
+      </c>
+      <c r="F3">
+        <v>-18.68</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>savanna</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>42.11</v>
+      </c>
+      <c r="E4">
+        <v>-25.868</v>
+      </c>
+      <c r="F4">
+        <v>-14.316</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>temperate grassland</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>118</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>10.17</v>
+      </c>
+      <c r="E5">
+        <v>-226.133</v>
+      </c>
+      <c r="F5">
+        <v>-6.61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tropical seasonal forest</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>135</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>5.19</v>
+      </c>
+      <c r="E6">
+        <v>-54.748</v>
+      </c>
+      <c r="F6">
+        <v>-42.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>boreal forest</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>13.51</v>
+      </c>
+      <c r="E7">
+        <v>-231.417</v>
+      </c>
+      <c r="F7">
+        <v>-82.078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>alpine</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>5.71</v>
+      </c>
+      <c r="E8">
+        <v>-65.86</v>
+      </c>
+      <c r="F8">
+        <v>-65.86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shrubland</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>7.69</v>
+      </c>
+      <c r="E9">
+        <v>-63.145</v>
+      </c>
+      <c r="F9">
+        <v>-63.145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>subtropical desert</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>14.29</v>
+      </c>
+      <c r="E10">
+        <v>-0.01</v>
+      </c>
+      <c r="F10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>desert</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>temperate rainforest</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tropical rainforest</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>woodland</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>